--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 PRONGHORN BUCK L.E.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 PRONGHORN BUCK L.E.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$67</definedName>
@@ -654,7 +654,11 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -723,7 +727,11 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -792,7 +800,11 @@
           <t>87.5</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
           <t>5.9</t>
@@ -861,7 +873,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>11.5</t>
@@ -930,7 +946,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -999,7 +1019,11 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>5.8</t>
@@ -1068,7 +1092,11 @@
           <t>10.0</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
@@ -1137,7 +1165,11 @@
           <t>86.7</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t>3.9</t>
@@ -1206,7 +1238,11 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>7.3</t>
@@ -1275,7 +1311,11 @@
           <t>93.5</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -1344,7 +1384,11 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
           <t>6.2</t>
@@ -1413,7 +1457,11 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>9.5</t>
@@ -1482,7 +1530,11 @@
           <t>75.0</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t>7.2</t>
@@ -1551,7 +1603,11 @@
           <t>77.8</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -1620,7 +1676,11 @@
           <t>36.8</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>7.1</t>
@@ -1689,7 +1749,11 @@
           <t>90.3</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -1758,7 +1822,11 @@
           <t>94.4</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -1827,7 +1895,11 @@
           <t>88.9</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
           <t>5.6</t>
@@ -1896,7 +1968,11 @@
           <t>60.9</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -1965,7 +2041,11 @@
           <t>71.4</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -2103,7 +2183,11 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
           <t>1.9</t>
@@ -2172,7 +2256,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t>1.5</t>
@@ -2241,7 +2329,11 @@
           <t>70.6</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -2310,7 +2402,11 @@
           <t>87.5</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -2379,7 +2475,11 @@
           <t>75.0</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -2586,7 +2686,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -2655,7 +2759,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -2724,7 +2832,11 @@
           <t>83.0</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -2793,7 +2905,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
           <t>1.8</t>
@@ -2862,7 +2978,11 @@
           <t>76.5</t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -2931,7 +3051,11 @@
           <t>92.3</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -3000,7 +3124,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -3069,7 +3197,11 @@
           <t>69.6</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -3138,7 +3270,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
           <t>1.8</t>
@@ -3207,7 +3343,11 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -3345,7 +3485,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -3414,7 +3558,11 @@
           <t>78.5</t>
         </is>
       </c>
-      <c r="N42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -3552,7 +3700,11 @@
           <t>94.9</t>
         </is>
       </c>
-      <c r="N44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -3690,7 +3842,11 @@
           <t>80.8</t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -3759,7 +3915,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
           <t>7.0</t>
@@ -3828,7 +3988,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -3897,7 +4061,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -3966,7 +4134,11 @@
           <t>86.4</t>
         </is>
       </c>
-      <c r="N50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
           <t>2.9</t>
@@ -4035,7 +4207,11 @@
           <t>74.2</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -4104,7 +4280,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
           <t>1.8</t>
@@ -4173,7 +4353,11 @@
           <t>87.5</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -4242,7 +4426,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="N54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -4311,7 +4499,11 @@
           <t>78.6</t>
         </is>
       </c>
-      <c r="N55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -4380,7 +4572,11 @@
           <t>58.3</t>
         </is>
       </c>
-      <c r="N56" s="3" t="inlineStr"/>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
           <t>2.9</t>
@@ -4518,7 +4714,11 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="N58" s="3" t="inlineStr"/>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -4587,7 +4787,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
           <t>7.5</t>
@@ -4656,7 +4860,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N60" s="3" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -4725,7 +4933,11 @@
           <t>96.1</t>
         </is>
       </c>
-      <c r="N61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -4794,7 +5006,11 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="N62" s="3" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -4863,7 +5079,11 @@
           <t>69.1</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
           <t>2.8</t>
@@ -5070,7 +5290,11 @@
           <t>87.5</t>
         </is>
       </c>
-      <c r="N66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -5139,7 +5363,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="N67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
           <t>9.3</t>
